--- a/files/vol_marks_legacy_format.xlsx
+++ b/files/vol_marks_legacy_format.xlsx
@@ -29,6 +29,7 @@
     <sheet name="PARAMS" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="Sales Margin" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="Vega Weights" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="EVENTS" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames>
     <definedName name="Z_64F0AAC0_1236_4FB2_9E8A_12AD3842C0BD_.wvu.FilterData" localSheetId="20" hidden="0" function="0" vbProcedure="0">'Sales Margin'!$A$1:$R$182</definedName>
@@ -45,7 +46,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* \-??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
@@ -55,6 +56,8 @@
     <numFmt numFmtId="170" formatCode="0.000%"/>
     <numFmt numFmtId="171" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
     <numFmt numFmtId="172" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="173" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="174" formatCode="yyyy-mm-dd hh:mm"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -280,7 +283,7 @@
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -459,6 +462,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="20">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -878,39 +882,39 @@
   <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.82421875" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="8.289999999999999" customWidth="1" style="29" min="2" max="2"/>
-    <col width="13.57" customWidth="1" style="29" min="11" max="11"/>
+    <col width="8.289999999999999" customWidth="1" style="30" min="2" max="2"/>
+    <col width="13.57" customWidth="1" style="30" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1" s="27">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>expiry</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>ST 10D</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>ST 25D</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>RR 25D</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>RR 10D</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1" s="27">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>1W</t>
         </is>
@@ -919,10 +923,10 @@
         <f>C2*3.4</f>
         <v>0.476</v>
       </c>
-      <c r="C2" s="29" t="n">
+      <c r="C2" s="30" t="n">
         <v>0.14</v>
       </c>
-      <c r="D2" s="29" t="n">
+      <c r="D2" s="30" t="n">
         <v>0.0475</v>
       </c>
       <c r="E2" s="41">
@@ -931,7 +935,7 @@
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1" s="27">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>2W</t>
         </is>
@@ -940,10 +944,10 @@
         <f>C3*3.4</f>
         <v>0.4675</v>
       </c>
-      <c r="C3" s="29" t="n">
+      <c r="C3" s="30" t="n">
         <v>0.1375</v>
       </c>
-      <c r="D3" s="29" t="n">
+      <c r="D3" s="30" t="n">
         <v>0.1225</v>
       </c>
       <c r="E3" s="41">
@@ -952,7 +956,7 @@
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1" s="27">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
@@ -961,10 +965,10 @@
         <f>C4*3.4</f>
         <v>0.5695</v>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="30" t="n">
         <v>0.1675</v>
       </c>
-      <c r="D4" s="29" t="n">
+      <c r="D4" s="30" t="n">
         <v>0.26</v>
       </c>
       <c r="E4" s="41">
@@ -973,7 +977,7 @@
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1" s="27">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>2M</t>
         </is>
@@ -982,10 +986,10 @@
         <f>C5*3.4</f>
         <v>0.663</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="30" t="n">
         <v>0.195</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="30" t="n">
         <v>0.36</v>
       </c>
       <c r="E5" s="41">
@@ -994,7 +998,7 @@
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1" s="27">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
@@ -1003,10 +1007,10 @@
         <f>C6*3.4</f>
         <v>0.765</v>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="30" t="n">
         <v>0.225</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="30" t="n">
         <v>0.4625</v>
       </c>
       <c r="E6" s="41">
@@ -1015,7 +1019,7 @@
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1" s="27">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
@@ -1024,10 +1028,10 @@
         <f>C7*3.4</f>
         <v>0.867</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="30" t="n">
         <v>0.255</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="30" t="n">
         <v>0.6775</v>
       </c>
       <c r="E7" s="41">
@@ -1036,7 +1040,7 @@
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1" s="27">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>9M</t>
         </is>
@@ -1045,10 +1049,10 @@
         <f>C8*3.4</f>
         <v>1.02</v>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="30" t="n">
         <v>0.3</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="30" t="n">
         <v>0.57</v>
       </c>
       <c r="E8" s="41">
@@ -1057,7 +1061,7 @@
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1" s="27">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
@@ -1066,10 +1070,10 @@
         <f>C9*3.4</f>
         <v>1.122</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="30" t="n">
         <v>0.33</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="30" t="n">
         <v>0.925</v>
       </c>
       <c r="E9" s="41">
@@ -1078,7 +1082,7 @@
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1" s="27">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>2Y</t>
         </is>
@@ -1087,10 +1091,10 @@
         <f>C10*3.4</f>
         <v>1.207</v>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="30" t="n">
         <v>0.355</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="30" t="n">
         <v>1.1225</v>
       </c>
       <c r="E10" s="41">
@@ -1133,34 +1137,34 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.82421875" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1" s="27">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>expiry</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>ST 10D</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>ST 25D</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>RR 25D</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>RR 10D</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1" s="27">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>1W</t>
         </is>
@@ -1169,10 +1173,10 @@
         <f>C2*3.25</f>
         <v>0.706875</v>
       </c>
-      <c r="C2" s="29" t="n">
+      <c r="C2" s="30" t="n">
         <v>0.2175</v>
       </c>
-      <c r="D2" s="29" t="n">
+      <c r="D2" s="30" t="n">
         <v>-1.25</v>
       </c>
       <c r="E2" s="43">
@@ -1181,7 +1185,7 @@
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1" s="27">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>2W</t>
         </is>
@@ -1190,10 +1194,10 @@
         <f>C3*3.25</f>
         <v>0.755625</v>
       </c>
-      <c r="C3" s="29" t="n">
+      <c r="C3" s="30" t="n">
         <v>0.2325</v>
       </c>
-      <c r="D3" s="29" t="n">
+      <c r="D3" s="30" t="n">
         <v>-1.2925</v>
       </c>
       <c r="E3" s="43">
@@ -1202,7 +1206,7 @@
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1" s="27">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>3W</t>
         </is>
@@ -1211,10 +1215,10 @@
         <f>C4*3.25</f>
         <v>1.105</v>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="30" t="n">
         <v>0.34</v>
       </c>
-      <c r="D4" s="29" t="n">
+      <c r="D4" s="30" t="n">
         <v>-1.2975</v>
       </c>
       <c r="E4" s="43">
@@ -1223,7 +1227,7 @@
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1" s="27">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
@@ -1232,10 +1236,10 @@
         <f>C5*3.75</f>
         <v>0.965625</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="30" t="n">
         <v>0.2575</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="30" t="n">
         <v>-1.47</v>
       </c>
       <c r="E5" s="43">
@@ -1244,7 +1248,7 @@
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1" s="27">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>2M</t>
         </is>
@@ -1253,10 +1257,10 @@
         <f>4*C6</f>
         <v>1.26</v>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="30" t="n">
         <v>0.315</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="30" t="n">
         <v>-1.84</v>
       </c>
       <c r="E6" s="43">
@@ -1265,7 +1269,7 @@
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1" s="27">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
@@ -1274,10 +1278,10 @@
         <f>4*C7</f>
         <v>1.41</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="30" t="n">
         <v>0.3525</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="30" t="n">
         <v>-2.1575</v>
       </c>
       <c r="E7" s="43">
@@ -1286,7 +1290,7 @@
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1" s="27">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
@@ -1295,10 +1299,10 @@
         <f>4*C8</f>
         <v>1.68</v>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="30" t="n">
         <v>0.42</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="30" t="n">
         <v>-2.5675</v>
       </c>
       <c r="E8" s="43">
@@ -1307,7 +1311,7 @@
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1" s="27">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>9M</t>
         </is>
@@ -1316,10 +1320,10 @@
         <f>4*C9</f>
         <v>1.87</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="30" t="n">
         <v>0.4675</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="30" t="n">
         <v>-2.735</v>
       </c>
       <c r="E9" s="43">
@@ -1328,7 +1332,7 @@
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1" s="27">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
@@ -1337,10 +1341,10 @@
         <f>4.25*C10</f>
         <v>2.135625</v>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="30" t="n">
         <v>0.5024999999999999</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="30" t="n">
         <v>-2.875</v>
       </c>
       <c r="E10" s="43">
@@ -1349,7 +1353,7 @@
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1" s="27">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>2Y</t>
         </is>
@@ -1358,10 +1362,10 @@
         <f>4.25*C11</f>
         <v>2.295</v>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="30" t="n">
         <v>0.54</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="30" t="n">
         <v>-3.34</v>
       </c>
       <c r="E11" s="43">
@@ -1386,34 +1390,34 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.82421875" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1" s="27">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>expiry</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>ST 10D</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>ST 25D</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>RR 25D</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>RR 10D</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1" s="27">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>1W</t>
         </is>
@@ -1422,10 +1426,10 @@
         <f>3.25*C2</f>
         <v>0.6175</v>
       </c>
-      <c r="C2" s="29" t="n">
+      <c r="C2" s="30" t="n">
         <v>0.19</v>
       </c>
-      <c r="D2" s="29" t="n">
+      <c r="D2" s="30" t="n">
         <v>-0.43</v>
       </c>
       <c r="E2" s="43">
@@ -1434,7 +1438,7 @@
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1" s="27">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>2W</t>
         </is>
@@ -1443,10 +1447,10 @@
         <f>3.25*C3</f>
         <v>0.65</v>
       </c>
-      <c r="C3" s="29" t="n">
+      <c r="C3" s="30" t="n">
         <v>0.2</v>
       </c>
-      <c r="D3" s="29" t="n">
+      <c r="D3" s="30" t="n">
         <v>-0.415</v>
       </c>
       <c r="E3" s="43">
@@ -1455,7 +1459,7 @@
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1" s="27">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>3W</t>
         </is>
@@ -1464,10 +1468,10 @@
         <f>3.25*C4</f>
         <v>0.6175</v>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="30" t="n">
         <v>0.19</v>
       </c>
-      <c r="D4" s="29" t="n">
+      <c r="D4" s="30" t="n">
         <v>-0.37</v>
       </c>
       <c r="E4" s="43">
@@ -1476,7 +1480,7 @@
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1" s="27">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
@@ -1485,10 +1489,10 @@
         <f>3.25*C5</f>
         <v>0.76375</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="30" t="n">
         <v>0.235</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="30" t="n">
         <v>-0.475</v>
       </c>
       <c r="E5" s="43">
@@ -1497,7 +1501,7 @@
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1" s="27">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>2M</t>
         </is>
@@ -1506,10 +1510,10 @@
         <f>3.25*C6</f>
         <v>0.869375</v>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="30" t="n">
         <v>0.2675</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="30" t="n">
         <v>-0.6625</v>
       </c>
       <c r="E6" s="43">
@@ -1518,7 +1522,7 @@
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1" s="27">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
@@ -1527,10 +1531,10 @@
         <f>3.25*C7</f>
         <v>0.950625</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="30" t="n">
         <v>0.2925</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="30" t="n">
         <v>-0.8275</v>
       </c>
       <c r="E7" s="43">
@@ -1539,7 +1543,7 @@
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1" s="27">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
@@ -1548,10 +1552,10 @@
         <f>3.25*C8</f>
         <v>1.129375</v>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="30" t="n">
         <v>0.3475</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="30" t="n">
         <v>-1.0925</v>
       </c>
       <c r="E8" s="43">
@@ -1560,7 +1564,7 @@
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1" s="27">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>9M</t>
         </is>
@@ -1569,10 +1573,10 @@
         <f>3.25*C9</f>
         <v>1.259375</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="30" t="n">
         <v>0.3875</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="30" t="n">
         <v>-1.2925</v>
       </c>
       <c r="E9" s="43">
@@ -1581,7 +1585,7 @@
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1" s="27">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
@@ -1590,10 +1594,10 @@
         <f>3.25*C10</f>
         <v>1.291875</v>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="30" t="n">
         <v>0.3975</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="30" t="n">
         <v>-1.3775</v>
       </c>
       <c r="E10" s="43">
@@ -1602,7 +1606,7 @@
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1" s="27">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>2Y</t>
         </is>
@@ -1611,10 +1615,10 @@
         <f>3.25*C11</f>
         <v>1.3975</v>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="30" t="n">
         <v>0.43</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="30" t="n">
         <v>-1.685</v>
       </c>
       <c r="E11" s="44">
@@ -1638,40 +1642,40 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.859375" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="6.42" customWidth="1" style="29" min="1" max="1"/>
-    <col width="7.71" customWidth="1" style="29" min="2" max="3"/>
-    <col width="7.87" customWidth="1" style="29" min="4" max="5"/>
+    <col width="6.42" customWidth="1" style="30" min="1" max="1"/>
+    <col width="7.71" customWidth="1" style="30" min="2" max="3"/>
+    <col width="7.87" customWidth="1" style="30" min="4" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1" s="27">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>expiry</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>ST 10D</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>ST 25D</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>RR 25D</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>RR 10D</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1" s="27">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>1W</t>
         </is>
@@ -1680,10 +1684,10 @@
         <f>C2*3</f>
         <v>0.4425</v>
       </c>
-      <c r="C2" s="29" t="n">
+      <c r="C2" s="30" t="n">
         <v>0.1475</v>
       </c>
-      <c r="D2" s="29" t="n">
+      <c r="D2" s="30" t="n">
         <v>-0.18</v>
       </c>
       <c r="E2" s="31">
@@ -1692,7 +1696,7 @@
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1" s="27">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>2W</t>
         </is>
@@ -1701,10 +1705,10 @@
         <f>C3*3</f>
         <v>0.4575</v>
       </c>
-      <c r="C3" s="29" t="n">
+      <c r="C3" s="30" t="n">
         <v>0.1525</v>
       </c>
-      <c r="D3" s="29" t="n">
+      <c r="D3" s="30" t="n">
         <v>-0.165</v>
       </c>
       <c r="E3" s="31">
@@ -1713,7 +1717,7 @@
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1" s="27">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>3W</t>
         </is>
@@ -1722,10 +1726,10 @@
         <f>C4*3</f>
         <v>0.4875</v>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="30" t="n">
         <v>0.1625</v>
       </c>
-      <c r="D4" s="29" t="n">
+      <c r="D4" s="30" t="n">
         <v>-0.1775</v>
       </c>
       <c r="E4" s="31">
@@ -1734,7 +1738,7 @@
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1" s="27">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
@@ -1743,10 +1747,10 @@
         <f>C5*3</f>
         <v>0.5175</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="30" t="n">
         <v>0.1725</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="30" t="n">
         <v>-0.1225</v>
       </c>
       <c r="E5" s="31">
@@ -1755,7 +1759,7 @@
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1" s="27">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>2M</t>
         </is>
@@ -1764,10 +1768,10 @@
         <f>C6*3</f>
         <v>0.585</v>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="30" t="n">
         <v>0.195</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="30" t="n">
         <v>-0.1025</v>
       </c>
       <c r="E6" s="31">
@@ -1776,7 +1780,7 @@
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1" s="27">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
@@ -1785,10 +1789,10 @@
         <f>C7*3</f>
         <v>0.6375</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="30" t="n">
         <v>0.2125</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="30" t="n">
         <v>-0.0925</v>
       </c>
       <c r="E7" s="31">
@@ -1797,7 +1801,7 @@
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1" s="27">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
@@ -1806,10 +1810,10 @@
         <f>C8*3.25</f>
         <v>0.8775</v>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="30" t="n">
         <v>0.27</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="30" t="n">
         <v>-0.04</v>
       </c>
       <c r="E8" s="31">
@@ -1818,7 +1822,7 @@
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1" s="27">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>9M</t>
         </is>
@@ -1827,10 +1831,10 @@
         <f>C9*3.5</f>
         <v>1.04125</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="30" t="n">
         <v>0.2975</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="30" t="n">
         <v>0.0025</v>
       </c>
       <c r="E9" s="31">
@@ -1839,7 +1843,7 @@
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1" s="27">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
@@ -1848,10 +1852,10 @@
         <f>C10*3.55</f>
         <v>1.144875</v>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="30" t="n">
         <v>0.3225</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="30" t="n">
         <v>0.025</v>
       </c>
       <c r="E10" s="31">
@@ -1860,7 +1864,7 @@
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1" s="27">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>2Y</t>
         </is>
@@ -1869,10 +1873,10 @@
         <f>C11*3.55</f>
         <v>1.207</v>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="30" t="n">
         <v>0.34</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="30" t="n">
         <v>-0.055</v>
       </c>
       <c r="E11" s="31">
@@ -1904,40 +1908,40 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.859375" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="6.42" customWidth="1" style="29" min="1" max="1"/>
-    <col width="7.71" customWidth="1" style="29" min="2" max="3"/>
-    <col width="7.87" customWidth="1" style="29" min="4" max="5"/>
+    <col width="6.42" customWidth="1" style="30" min="1" max="1"/>
+    <col width="7.71" customWidth="1" style="30" min="2" max="3"/>
+    <col width="7.87" customWidth="1" style="30" min="4" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1" s="27">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>expiry</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>ST 10D</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>ST 25D</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>RR 25D</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>RR 10D</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1" s="27">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>1W</t>
         </is>
@@ -1946,10 +1950,10 @@
         <f>C2*3</f>
         <v>0.8175</v>
       </c>
-      <c r="C2" s="29" t="n">
+      <c r="C2" s="30" t="n">
         <v>0.2725</v>
       </c>
-      <c r="D2" s="29" t="n">
+      <c r="D2" s="30" t="n">
         <v>-0.9175</v>
       </c>
       <c r="E2" s="43">
@@ -1958,7 +1962,7 @@
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1" s="27">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>2W</t>
         </is>
@@ -1967,10 +1971,10 @@
         <f>C3*3</f>
         <v>0.8775</v>
       </c>
-      <c r="C3" s="29" t="n">
+      <c r="C3" s="30" t="n">
         <v>0.2925</v>
       </c>
-      <c r="D3" s="29" t="n">
+      <c r="D3" s="30" t="n">
         <v>-1.0425</v>
       </c>
       <c r="E3" s="43">
@@ -1979,7 +1983,7 @@
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1" s="27">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>3W</t>
         </is>
@@ -1988,10 +1992,10 @@
         <f>C4*3</f>
         <v>0.93</v>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="30" t="n">
         <v>0.31</v>
       </c>
-      <c r="D4" s="29" t="n">
+      <c r="D4" s="30" t="n">
         <v>-1.205</v>
       </c>
       <c r="E4" s="43">
@@ -2000,7 +2004,7 @@
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1" s="27">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
@@ -2009,10 +2013,10 @@
         <f>C5*3</f>
         <v>1.02</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="30" t="n">
         <v>0.34</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="30" t="n">
         <v>-1.295</v>
       </c>
       <c r="E5" s="43">
@@ -2021,7 +2025,7 @@
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1" s="27">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>2M</t>
         </is>
@@ -2030,10 +2034,10 @@
         <f>C6*3</f>
         <v>1.11</v>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="30" t="n">
         <v>0.37</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="30" t="n">
         <v>-1.425</v>
       </c>
       <c r="E6" s="43">
@@ -2042,7 +2046,7 @@
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1" s="27">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
@@ -2051,10 +2055,10 @@
         <f>C7*3</f>
         <v>1.1925</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="30" t="n">
         <v>0.3975</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="30" t="n">
         <v>-1.4875</v>
       </c>
       <c r="E7" s="43">
@@ -2063,7 +2067,7 @@
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1" s="27">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
@@ -2072,10 +2076,10 @@
         <f>C8*3</f>
         <v>1.3125</v>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="30" t="n">
         <v>0.4375</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="30" t="n">
         <v>-1.6475</v>
       </c>
       <c r="E8" s="43">
@@ -2084,7 +2088,7 @@
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1" s="27">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>9M</t>
         </is>
@@ -2093,10 +2097,10 @@
         <f>C9*3</f>
         <v>1.3575</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="30" t="n">
         <v>0.4525</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="30" t="n">
         <v>-1.7175</v>
       </c>
       <c r="E9" s="43">
@@ -2105,7 +2109,7 @@
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1" s="27">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
@@ -2114,10 +2118,10 @@
         <f>C10*3</f>
         <v>1.4025</v>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="30" t="n">
         <v>0.4675</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="30" t="n">
         <v>-1.7675</v>
       </c>
       <c r="E10" s="43">
@@ -2126,7 +2130,7 @@
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1" s="27">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>2Y</t>
         </is>
@@ -2135,10 +2139,10 @@
         <f>C11*3</f>
         <v>1.47</v>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="30" t="n">
         <v>0.49</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="30" t="n">
         <v>-1.75</v>
       </c>
       <c r="E11" s="43">
@@ -2170,40 +2174,40 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.859375" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="6.42" customWidth="1" style="29" min="1" max="1"/>
-    <col width="7.71" customWidth="1" style="29" min="2" max="3"/>
-    <col width="7.87" customWidth="1" style="29" min="4" max="5"/>
+    <col width="6.42" customWidth="1" style="30" min="1" max="1"/>
+    <col width="7.71" customWidth="1" style="30" min="2" max="3"/>
+    <col width="7.87" customWidth="1" style="30" min="4" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1" s="27">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>expiry</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>ST 10D</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>ST 25D</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>RR 25D</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>RR 10D</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1" s="27">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>1W</t>
         </is>
@@ -2212,10 +2216,10 @@
         <f>C2*3</f>
         <v>0.6525</v>
       </c>
-      <c r="C2" s="29" t="n">
+      <c r="C2" s="30" t="n">
         <v>0.2175</v>
       </c>
-      <c r="D2" s="29" t="n">
+      <c r="D2" s="30" t="n">
         <v>-0.0275</v>
       </c>
       <c r="E2" s="31">
@@ -2224,7 +2228,7 @@
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1" s="27">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>2W</t>
         </is>
@@ -2233,10 +2237,10 @@
         <f>C3*3</f>
         <v>0.675</v>
       </c>
-      <c r="C3" s="29" t="n">
+      <c r="C3" s="30" t="n">
         <v>0.225</v>
       </c>
-      <c r="D3" s="29" t="n">
+      <c r="D3" s="30" t="n">
         <v>-0.11</v>
       </c>
       <c r="E3" s="31">
@@ -2245,7 +2249,7 @@
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1" s="27">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>3W</t>
         </is>
@@ -2254,10 +2258,10 @@
         <f>C4*3</f>
         <v>0.735</v>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="30" t="n">
         <v>0.245</v>
       </c>
-      <c r="D4" s="29" t="n">
+      <c r="D4" s="30" t="n">
         <v>-0.1475</v>
       </c>
       <c r="E4" s="31">
@@ -2266,7 +2270,7 @@
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1" s="27">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
@@ -2275,10 +2279,10 @@
         <f>C5*3</f>
         <v>0.72</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="30" t="n">
         <v>0.24</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="30" t="n">
         <v>-0.24</v>
       </c>
       <c r="E5" s="31">
@@ -2287,7 +2291,7 @@
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1" s="27">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>2M</t>
         </is>
@@ -2296,10 +2300,10 @@
         <f>C6*3</f>
         <v>0.8025</v>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="30" t="n">
         <v>0.2675</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="30" t="n">
         <v>-0.4575</v>
       </c>
       <c r="E6" s="31">
@@ -2308,7 +2312,7 @@
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1" s="27">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
@@ -2317,10 +2321,10 @@
         <f>C7*3</f>
         <v>0.87</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="30" t="n">
         <v>0.29</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="30" t="n">
         <v>-0.645</v>
       </c>
       <c r="E7" s="31">
@@ -2329,7 +2333,7 @@
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1" s="27">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
@@ -2338,10 +2342,10 @@
         <f>C8*3</f>
         <v>0.99</v>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="30" t="n">
         <v>0.33</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="30" t="n">
         <v>-0.9575</v>
       </c>
       <c r="E8" s="44">
@@ -2350,7 +2354,7 @@
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1" s="27">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>9M</t>
         </is>
@@ -2359,10 +2363,10 @@
         <f>C9*3</f>
         <v>1.065</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="30" t="n">
         <v>0.355</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="30" t="n">
         <v>-1.0925</v>
       </c>
       <c r="E9" s="31">
@@ -2371,7 +2375,7 @@
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1" s="27">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
@@ -2380,10 +2384,10 @@
         <f>3.25*C10</f>
         <v>1.2025</v>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="30" t="n">
         <v>0.37</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="30" t="n">
         <v>-1.19</v>
       </c>
       <c r="E10" s="31">
@@ -2392,7 +2396,7 @@
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1" s="27">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>2Y</t>
         </is>
@@ -2401,10 +2405,10 @@
         <f>3.5*C11</f>
         <v>1.4525</v>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="30" t="n">
         <v>0.415</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="30" t="n">
         <v>-1.42</v>
       </c>
       <c r="E11" s="31">
@@ -2436,44 +2440,44 @@
   <dimension ref="A1:U30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.859375" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="6.42" customWidth="1" style="29" min="1" max="1"/>
-    <col width="7.71" customWidth="1" style="29" min="2" max="3"/>
-    <col width="7.87" customWidth="1" style="29" min="4" max="5"/>
-    <col width="10.29" customWidth="1" style="29" min="8" max="8"/>
-    <col width="12.86" customWidth="1" style="29" min="12" max="12"/>
-    <col width="15" customWidth="1" style="29" min="13" max="13"/>
-    <col width="12.86" customWidth="1" style="29" min="15" max="15"/>
+    <col width="6.42" customWidth="1" style="30" min="1" max="1"/>
+    <col width="7.71" customWidth="1" style="30" min="2" max="3"/>
+    <col width="7.87" customWidth="1" style="30" min="4" max="5"/>
+    <col width="10.29" customWidth="1" style="30" min="8" max="8"/>
+    <col width="12.86" customWidth="1" style="30" min="12" max="12"/>
+    <col width="15" customWidth="1" style="30" min="13" max="13"/>
+    <col width="12.86" customWidth="1" style="30" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1" s="27">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>expiry</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>ST 10D</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>ST 25D</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>RR 25D</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>RR 10D</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1" s="27">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>1W</t>
         </is>
@@ -2494,7 +2498,7 @@
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1" s="27">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>2W</t>
         </is>
@@ -2515,7 +2519,7 @@
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1" s="27">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
@@ -2536,7 +2540,7 @@
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1" s="27">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>2M</t>
         </is>
@@ -2557,7 +2561,7 @@
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1" s="27">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
@@ -2579,7 +2583,7 @@
       <c r="L6" s="48" t="n"/>
     </row>
     <row r="7" ht="12.75" customHeight="1" s="27">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
@@ -2600,7 +2604,7 @@
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1" s="27">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>9M</t>
         </is>
@@ -2622,7 +2626,7 @@
       <c r="L8" s="49" t="n"/>
     </row>
     <row r="9" ht="12.75" customHeight="1" s="27">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
@@ -2644,7 +2648,7 @@
       <c r="O9" s="50" t="n"/>
     </row>
     <row r="10" ht="12.75" customHeight="1" s="27">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>2Y</t>
         </is>
@@ -2723,34 +2727,34 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.82421875" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1" s="27">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>expiry</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>ST 10D</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>ST 25D</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>RR 25D</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>RR 10D</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1" s="27">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>1W</t>
         </is>
@@ -2771,7 +2775,7 @@
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1" s="27">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>2W</t>
         </is>
@@ -2792,7 +2796,7 @@
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1" s="27">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
@@ -2813,7 +2817,7 @@
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1" s="27">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>2M</t>
         </is>
@@ -2834,7 +2838,7 @@
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1" s="27">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
@@ -2855,7 +2859,7 @@
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1" s="27">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
@@ -2876,7 +2880,7 @@
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1" s="27">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>9M</t>
         </is>
@@ -2897,7 +2901,7 @@
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1" s="27">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
@@ -2918,7 +2922,7 @@
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1" s="27">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>2Y</t>
         </is>
@@ -2955,221 +2959,221 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.82421875" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1" s="27">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>BASE</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>COR</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>AUDJPY</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>EURJPY</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>EURCNH</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" s="30" t="inlineStr">
         <is>
           <t>GBPNZD</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" s="30" t="inlineStr">
         <is>
           <t>EURGBP</t>
         </is>
       </c>
-      <c r="H1" s="29" t="inlineStr">
+      <c r="H1" s="30" t="inlineStr">
         <is>
           <t>GBPCNH</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="I1" s="30" t="inlineStr">
         <is>
           <t>TENORS</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1" s="27">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>USDCNH</t>
         </is>
       </c>
-      <c r="B2" s="29" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>AUDJPY</t>
         </is>
       </c>
-      <c r="C2" s="29" t="inlineStr">
+      <c r="C2" s="30" t="inlineStr">
         <is>
           <t>AUDUSD</t>
         </is>
       </c>
-      <c r="D2" s="29" t="inlineStr">
+      <c r="D2" s="30" t="inlineStr">
         <is>
           <t>EURUSD</t>
         </is>
       </c>
-      <c r="E2" s="29" t="inlineStr">
+      <c r="E2" s="30" t="inlineStr">
         <is>
           <t>EURUSD</t>
         </is>
       </c>
-      <c r="F2" s="29" t="inlineStr">
+      <c r="F2" s="30" t="inlineStr">
         <is>
           <t>GBPUSD</t>
         </is>
       </c>
-      <c r="G2" s="29" t="inlineStr">
+      <c r="G2" s="30" t="inlineStr">
         <is>
           <t>EURUSD</t>
         </is>
       </c>
-      <c r="H2" s="29" t="inlineStr">
+      <c r="H2" s="30" t="inlineStr">
         <is>
           <t>GBPUSD</t>
         </is>
       </c>
-      <c r="I2" s="29" t="inlineStr">
+      <c r="I2" s="30" t="inlineStr">
         <is>
           <t>1w</t>
         </is>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1" s="27">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>USDCNY</t>
         </is>
       </c>
-      <c r="B3" s="29" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>EURJPY</t>
         </is>
       </c>
-      <c r="C3" s="29" t="inlineStr">
+      <c r="C3" s="30" t="inlineStr">
         <is>
           <t>USDJPY</t>
         </is>
       </c>
-      <c r="D3" s="29" t="inlineStr">
+      <c r="D3" s="30" t="inlineStr">
         <is>
           <t>USDJPY</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="E3" s="30" t="inlineStr">
         <is>
           <t>USDCNH</t>
         </is>
       </c>
-      <c r="F3" s="29" t="inlineStr">
+      <c r="F3" s="30" t="inlineStr">
         <is>
           <t>NZDUSD</t>
         </is>
       </c>
-      <c r="G3" s="29" t="inlineStr">
+      <c r="G3" s="30" t="inlineStr">
         <is>
           <t>GBPUSD</t>
         </is>
       </c>
-      <c r="H3" s="29" t="inlineStr">
+      <c r="H3" s="30" t="inlineStr">
         <is>
           <t>USDCNH</t>
         </is>
       </c>
-      <c r="I3" s="29" t="inlineStr">
+      <c r="I3" s="30" t="inlineStr">
         <is>
           <t>2w</t>
         </is>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1" s="27">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>USDJPY</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>EURCNH</t>
         </is>
       </c>
-      <c r="I4" s="29" t="inlineStr">
+      <c r="I4" s="30" t="inlineStr">
         <is>
           <t>3w</t>
         </is>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1" s="27">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>AUDUSD</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>GBPNZD</t>
         </is>
       </c>
-      <c r="I5" s="29" t="inlineStr">
+      <c r="I5" s="30" t="inlineStr">
         <is>
           <t>1m</t>
         </is>
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1" s="27">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>EURUSD</t>
         </is>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>EURGBP</t>
         </is>
       </c>
-      <c r="I6" s="29" t="inlineStr">
+      <c r="I6" s="30" t="inlineStr">
         <is>
           <t>2m</t>
         </is>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1" s="27">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>GBPUSD</t>
         </is>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>GBPCNH</t>
         </is>
       </c>
-      <c r="I7" s="29" t="inlineStr">
+      <c r="I7" s="30" t="inlineStr">
         <is>
           <t>3m</t>
         </is>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1" s="27">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>NZDUSD</t>
         </is>
       </c>
-      <c r="I8" s="29" t="inlineStr">
+      <c r="I8" s="30" t="inlineStr">
         <is>
           <t>6m</t>
         </is>
@@ -3181,14 +3185,14 @@
           <t>USDHKD</t>
         </is>
       </c>
-      <c r="I9" s="29" t="inlineStr">
+      <c r="I9" s="30" t="inlineStr">
         <is>
           <t>9m</t>
         </is>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1" s="27">
-      <c r="I10" s="29" t="inlineStr">
+      <c r="I10" s="30" t="inlineStr">
         <is>
           <t>1y</t>
         </is>
@@ -3207,32 +3211,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.78515625" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="15.15" customWidth="1" style="55" min="1" max="1"/>
-    <col width="10.85" customWidth="1" style="29" min="2" max="5"/>
+    <col width="10.85" customWidth="1" style="30" min="2" max="5"/>
     <col width="10.85" customWidth="1" style="56" min="6" max="6"/>
-    <col width="10.85" customWidth="1" style="29" min="7" max="14"/>
+    <col width="10.85" customWidth="1" style="30" min="7" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1" s="27">
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>USDCNH</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>USDCNY</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>EURCNH</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>GBPCNH</t>
         </is>
@@ -3242,42 +3246,42 @@
           <t>USDJPY</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" s="30" t="inlineStr">
         <is>
           <t>EURUSD</t>
         </is>
       </c>
-      <c r="H1" s="29" t="inlineStr">
+      <c r="H1" s="30" t="inlineStr">
         <is>
           <t>AUDUSD</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="I1" s="30" t="inlineStr">
         <is>
           <t>GBPUSD</t>
         </is>
       </c>
-      <c r="J1" s="29" t="inlineStr">
+      <c r="J1" s="30" t="inlineStr">
         <is>
           <t>NZDUSD</t>
         </is>
       </c>
-      <c r="K1" s="29" t="inlineStr">
+      <c r="K1" s="30" t="inlineStr">
         <is>
           <t>AUDJPY</t>
         </is>
       </c>
-      <c r="L1" s="29" t="inlineStr">
+      <c r="L1" s="30" t="inlineStr">
         <is>
           <t>EURJPY</t>
         </is>
       </c>
-      <c r="M1" s="29" t="inlineStr">
+      <c r="M1" s="30" t="inlineStr">
         <is>
           <t>GBPNZD</t>
         </is>
       </c>
-      <c r="N1" s="29" t="inlineStr">
+      <c r="N1" s="30" t="inlineStr">
         <is>
           <t>EURGBP</t>
         </is>
@@ -3294,43 +3298,43 @@
           <t>initial</t>
         </is>
       </c>
-      <c r="B2" s="29" t="n">
+      <c r="B2" s="30" t="n">
         <v>4.9</v>
       </c>
-      <c r="C2" s="29" t="n">
+      <c r="C2" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="D2" s="29" t="n">
+      <c r="D2" s="30" t="n">
         <v>0.42</v>
       </c>
-      <c r="E2" s="29" t="n">
+      <c r="E2" s="30" t="n">
         <v>0.5</v>
       </c>
       <c r="F2" s="56" t="n">
         <v>6.05</v>
       </c>
-      <c r="G2" s="29" t="n">
+      <c r="G2" s="30" t="n">
         <v>6.25</v>
       </c>
-      <c r="H2" s="29" t="n">
+      <c r="H2" s="30" t="n">
         <v>10.9</v>
       </c>
-      <c r="I2" s="29" t="n">
+      <c r="I2" s="30" t="n">
         <v>7.75</v>
       </c>
-      <c r="J2" s="29" t="n">
+      <c r="J2" s="30" t="n">
         <v>10.9</v>
       </c>
-      <c r="K2" s="29" t="n">
+      <c r="K2" s="30" t="n">
         <v>0.37</v>
       </c>
-      <c r="L2" s="29" t="n">
+      <c r="L2" s="30" t="n">
         <v>0.405</v>
       </c>
-      <c r="M2" s="29" t="n">
+      <c r="M2" s="30" t="n">
         <v>0.705</v>
       </c>
-      <c r="N2" s="29" t="n">
+      <c r="N2" s="30" t="n">
         <v>0.57</v>
       </c>
       <c r="O2" s="30" t="n">
@@ -3343,43 +3347,43 @@
           <t>long term</t>
         </is>
       </c>
-      <c r="B3" s="29" t="n">
+      <c r="B3" s="30" t="n">
         <v>6.8</v>
       </c>
-      <c r="C3" s="29" t="n">
+      <c r="C3" s="30" t="n">
         <v>4.95</v>
       </c>
-      <c r="D3" s="29" t="n">
+      <c r="D3" s="30" t="n">
         <v>0.39</v>
       </c>
-      <c r="E3" s="29" t="n">
+      <c r="E3" s="30" t="n">
         <v>0.375</v>
       </c>
       <c r="F3" s="56" t="n">
         <v>7.65</v>
       </c>
-      <c r="G3" s="29" t="n">
+      <c r="G3" s="30" t="n">
         <v>6.95</v>
       </c>
-      <c r="H3" s="29" t="n">
+      <c r="H3" s="30" t="n">
         <v>10.65</v>
       </c>
-      <c r="I3" s="29" t="n">
+      <c r="I3" s="30" t="n">
         <v>9.029999999999999</v>
       </c>
-      <c r="J3" s="29" t="n">
+      <c r="J3" s="30" t="n">
         <v>10.77</v>
       </c>
-      <c r="K3" s="29" t="n">
+      <c r="K3" s="30" t="n">
         <v>0.19</v>
       </c>
-      <c r="L3" s="29" t="n">
+      <c r="L3" s="30" t="n">
         <v>0.395</v>
       </c>
-      <c r="M3" s="29" t="n">
+      <c r="M3" s="30" t="n">
         <v>0.54</v>
       </c>
-      <c r="N3" s="29" t="n">
+      <c r="N3" s="30" t="n">
         <v>0.54</v>
       </c>
       <c r="O3" s="30" t="n">
@@ -3392,43 +3396,43 @@
           <t>ratevol</t>
         </is>
       </c>
-      <c r="B4" s="29" t="n">
+      <c r="B4" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="29" t="n">
+      <c r="D4" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="29" t="n">
+      <c r="E4" s="30" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="29" t="n">
+      <c r="G4" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="29" t="n">
+      <c r="H4" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="29" t="n">
+      <c r="I4" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="29" t="n">
+      <c r="J4" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="29" t="n">
+      <c r="K4" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="29" t="n">
+      <c r="L4" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="M4" s="29" t="n">
+      <c r="M4" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="N4" s="29" t="n">
+      <c r="N4" s="30" t="n">
         <v>0</v>
       </c>
       <c r="O4" s="30" t="n">
@@ -3441,43 +3445,43 @@
           <t>addon</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n">
+      <c r="B5" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="30" t="n">
         <v>-0.25</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="30" t="n">
         <v>0.6</v>
       </c>
       <c r="F5" s="56" t="n">
         <v>0.7</v>
       </c>
-      <c r="G5" s="29" t="n">
+      <c r="G5" s="30" t="n">
         <v>0.6</v>
       </c>
-      <c r="H5" s="29" t="n">
+      <c r="H5" s="30" t="n">
         <v>1.1</v>
       </c>
-      <c r="I5" s="29" t="n">
+      <c r="I5" s="30" t="n">
         <v>0.8</v>
       </c>
-      <c r="J5" s="29" t="n">
+      <c r="J5" s="30" t="n">
         <v>1.2</v>
       </c>
-      <c r="K5" s="29" t="n">
+      <c r="K5" s="30" t="n">
         <v>1.5</v>
       </c>
-      <c r="L5" s="29" t="n">
+      <c r="L5" s="30" t="n">
         <v>-0.2</v>
       </c>
-      <c r="M5" s="29" t="n">
+      <c r="M5" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="N5" s="29" t="n">
+      <c r="N5" s="30" t="n">
         <v>0</v>
       </c>
       <c r="O5" s="30" t="n">
@@ -3490,43 +3494,43 @@
           <t>MR</t>
         </is>
       </c>
-      <c r="B6" s="29" t="n">
+      <c r="B6" s="30" t="n">
         <v>4.5</v>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="30" t="n">
         <v>3.5</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="29" t="n">
+      <c r="E6" s="30" t="n">
         <v>3</v>
       </c>
       <c r="F6" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="29" t="n">
+      <c r="G6" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="H6" s="29" t="n">
+      <c r="H6" s="30" t="n">
         <v>6.5</v>
       </c>
-      <c r="I6" s="29" t="n">
+      <c r="I6" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="J6" s="29" t="n">
+      <c r="J6" s="30" t="n">
         <v>6.5</v>
       </c>
-      <c r="K6" s="29" t="n">
+      <c r="K6" s="30" t="n">
         <v>5.5</v>
       </c>
-      <c r="L6" s="29" t="n">
+      <c r="L6" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="M6" s="29" t="n">
+      <c r="M6" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="N6" s="29" t="n">
+      <c r="N6" s="30" t="n">
         <v>4</v>
       </c>
       <c r="O6" s="30" t="n">
@@ -3539,43 +3543,43 @@
           <t>rate corr</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="30" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="29" t="n">
+      <c r="G7" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="29" t="n">
+      <c r="H7" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="29" t="n">
+      <c r="I7" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="29" t="n">
+      <c r="J7" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="29" t="n">
+      <c r="K7" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="29" t="n">
+      <c r="L7" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="M7" s="29" t="n">
+      <c r="M7" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="N7" s="29" t="n">
+      <c r="N7" s="30" t="n">
         <v>0</v>
       </c>
       <c r="O7" s="30" t="n">
@@ -3588,186 +3592,90 @@
           <t>short decay</t>
         </is>
       </c>
-      <c r="B8" s="29" t="n">
+      <c r="B8" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="30" t="n">
         <v>50</v>
       </c>
       <c r="F8" s="56" t="n">
         <v>50</v>
       </c>
-      <c r="G8" s="29" t="n">
+      <c r="G8" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="H8" s="29" t="n">
+      <c r="H8" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="I8" s="29" t="n">
+      <c r="I8" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="J8" s="29" t="n">
+      <c r="J8" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="K8" s="29" t="n">
+      <c r="K8" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="L8" s="29" t="n">
+      <c r="L8" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="M8" s="29" t="n">
+      <c r="M8" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="N8" s="29" t="n">
+      <c r="N8" s="30" t="n">
         <v>50</v>
       </c>
       <c r="O8" s="30" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="9" ht="12.75" customFormat="1" customHeight="1" s="29">
-      <c r="A9" s="55" t="inlineStr">
-        <is>
-          <t>02/02/2024 00:00</t>
-        </is>
-      </c>
-      <c r="B9" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="29" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G9" s="29" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H9" s="29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I9" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="J9" s="29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K9" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="12.75" customFormat="1" customHeight="1" s="29">
-      <c r="A10" s="55" t="inlineStr">
-        <is>
-          <t>02/02/2024 10:00</t>
-        </is>
-      </c>
-      <c r="B10" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="29" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G10" s="29" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H10" s="29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I10" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="J10" s="29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K10" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11"/>
+    <row r="9" ht="12.75" customFormat="1" customHeight="1" s="30"/>
+    <row r="10" ht="12.75" customFormat="1" customHeight="1" s="30"/>
+    <row r="11">
+      <c r="E11" s="49" t="n"/>
+    </row>
     <row r="12"/>
-    <row r="13" ht="12.75" customHeight="1" s="27">
-      <c r="E13" s="49" t="n"/>
-    </row>
-    <row r="14"/>
-    <row r="15"/>
+    <row r="13" ht="12.75" customHeight="1" s="27"/>
+    <row r="14">
+      <c r="S14" s="57" t="n"/>
+    </row>
+    <row r="15">
+      <c r="P15" s="49" t="n"/>
+    </row>
     <row r="16" ht="15" customHeight="1" s="27">
-      <c r="S16" s="57" t="n"/>
+      <c r="P16" s="49" t="n"/>
     </row>
     <row r="17" ht="12.75" customHeight="1" s="27">
       <c r="P17" s="49" t="n"/>
     </row>
     <row r="18" ht="12.75" customHeight="1" s="27">
-      <c r="P18" s="49" t="n"/>
+      <c r="E18" s="49" t="n"/>
     </row>
     <row r="19" ht="12.75" customHeight="1" s="27">
-      <c r="P19" s="49" t="n"/>
+      <c r="E19" s="49" t="n"/>
     </row>
     <row r="20" ht="12.75" customHeight="1" s="27">
       <c r="E20" s="49" t="n"/>
     </row>
     <row r="21" ht="12.75" customHeight="1" s="27">
       <c r="E21" s="49" t="n"/>
-    </row>
-    <row r="22" ht="12.75" customHeight="1" s="27">
-      <c r="E22" s="49" t="n"/>
-    </row>
+      <c r="I21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="12.75" customHeight="1" s="27"/>
     <row r="23" ht="12.75" customHeight="1" s="27">
-      <c r="E23" s="49" t="n"/>
-      <c r="I23" s="49" t="n"/>
-    </row>
-    <row r="24"/>
-    <row r="25" ht="12.75" customHeight="1" s="27">
-      <c r="M25" s="49" t="n"/>
-    </row>
-    <row r="26" ht="12.75" customHeight="1" s="27">
-      <c r="M26" s="49" t="n"/>
-    </row>
+      <c r="M23" s="49" t="n"/>
+    </row>
+    <row r="24">
+      <c r="M24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="12.75" customHeight="1" s="27"/>
+    <row r="26" ht="12.75" customHeight="1" s="27"/>
     <row r="1048576" ht="12.8" customHeight="1" s="27"/>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -3796,8 +3704,8 @@
     <col width="15.15" customWidth="1" style="58" min="1" max="1"/>
     <col width="11.3" customWidth="1" style="49" min="2" max="2"/>
     <col width="12.86" customWidth="1" style="49" min="3" max="3"/>
-    <col width="11.57" customWidth="1" style="29" min="6" max="6"/>
-    <col width="12.86" customWidth="1" style="29" min="13" max="13"/>
+    <col width="11.57" customWidth="1" style="30" min="6" max="6"/>
+    <col width="12.86" customWidth="1" style="30" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1" s="27">
@@ -3864,7 +3772,7 @@
         <f>C4+B5</f>
         <v>1922914.0</v>
       </c>
-      <c r="E5" s="29" t="n"/>
+      <c r="E5" s="30" t="n"/>
     </row>
     <row r="6" ht="12.75" customHeight="1" s="27">
       <c r="A6" s="58" t="n">
@@ -3877,7 +3785,7 @@
         <f>C5+B6</f>
         <v>1928241.0</v>
       </c>
-      <c r="E6" s="29" t="n"/>
+      <c r="E6" s="30" t="n"/>
       <c r="N6" s="49" t="n"/>
     </row>
     <row r="7" ht="12.75" customHeight="1" s="27">
@@ -4318,7 +4226,7 @@
   <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.82421875" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="9.85" customWidth="1" style="29" min="2" max="2"/>
+    <col width="9.85" customWidth="1" style="30" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1" s="27">
@@ -4433,6 +4341,138 @@
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>USDCNH</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>USDCNY</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>EURCNH</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>GBPCNH</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>AUDUSD</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>AUDJPY</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>GBPNZD</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>USDHKD</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="60" t="n">
+        <v>45324</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="60" t="n">
+        <v>45324.41666666666</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -4446,34 +4486,34 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.82421875" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1" s="27">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>expiry</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>ST 10D</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>ST 25D</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>RR 25D</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>RR 10D</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1" s="27">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>1W</t>
         </is>
@@ -4482,10 +4522,10 @@
         <f>C2*2.8</f>
         <v>0.756</v>
       </c>
-      <c r="C2" s="29" t="n">
+      <c r="C2" s="30" t="n">
         <v>0.27</v>
       </c>
-      <c r="D2" s="29" t="n">
+      <c r="D2" s="30" t="n">
         <v>-0.955</v>
       </c>
       <c r="E2" s="31">
@@ -4494,7 +4534,7 @@
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1" s="27">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>2W</t>
         </is>
@@ -4503,10 +4543,10 @@
         <f>C3*2.8</f>
         <v>0.791</v>
       </c>
-      <c r="C3" s="29" t="n">
+      <c r="C3" s="30" t="n">
         <v>0.2825</v>
       </c>
-      <c r="D3" s="29" t="n">
+      <c r="D3" s="30" t="n">
         <v>-1.0825</v>
       </c>
       <c r="E3" s="31">
@@ -4515,7 +4555,7 @@
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1" s="27">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>3W</t>
         </is>
@@ -4524,10 +4564,10 @@
         <f>C4*2.8</f>
         <v>0.847</v>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="30" t="n">
         <v>0.3025</v>
       </c>
-      <c r="D4" s="29" t="n">
+      <c r="D4" s="30" t="n">
         <v>-1.24</v>
       </c>
       <c r="E4" s="31">
@@ -4536,7 +4576,7 @@
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1" s="27">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
@@ -4545,10 +4585,10 @@
         <f>C5*2.9</f>
         <v>0.90625</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="30" t="n">
         <v>0.3125</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="30" t="n">
         <v>-1.21</v>
       </c>
       <c r="E5" s="31">
@@ -4557,7 +4597,7 @@
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1" s="27">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>2M</t>
         </is>
@@ -4566,10 +4606,10 @@
         <f>C6*3</f>
         <v>1.05</v>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="30" t="n">
         <v>0.35</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="30" t="n">
         <v>-1.34</v>
       </c>
       <c r="E6" s="31">
@@ -4578,7 +4618,7 @@
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1" s="27">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
@@ -4587,10 +4627,10 @@
         <f>C7*3</f>
         <v>1.125</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="30" t="n">
         <v>0.375</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="30" t="n">
         <v>-1.455</v>
       </c>
       <c r="E7" s="31">
@@ -4599,7 +4639,7 @@
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1" s="27">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
@@ -4608,10 +4648,10 @@
         <f>C8*3.1</f>
         <v>1.26325</v>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="30" t="n">
         <v>0.4075</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="30" t="n">
         <v>-1.59</v>
       </c>
       <c r="E8" s="31">
@@ -4620,7 +4660,7 @@
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1" s="27">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>9M</t>
         </is>
@@ -4629,10 +4669,10 @@
         <f>C9*3.1</f>
         <v>1.333</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="30" t="n">
         <v>0.43</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="30" t="n">
         <v>-1.65</v>
       </c>
       <c r="E9" s="31">
@@ -4641,7 +4681,7 @@
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1" s="27">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
@@ -4650,10 +4690,10 @@
         <f>C10*3.2</f>
         <v>1.416</v>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="30" t="n">
         <v>0.4425</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="30" t="n">
         <v>-1.71</v>
       </c>
       <c r="E10" s="31">
@@ -4662,7 +4702,7 @@
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1" s="27">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>2Y</t>
         </is>
@@ -4671,10 +4711,10 @@
         <f>C11*3.5</f>
         <v>1.46125</v>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="30" t="n">
         <v>0.4175</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="30" t="n">
         <v>-1.8525</v>
       </c>
       <c r="E11" s="31">
@@ -4699,34 +4739,34 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.82421875" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1" s="27">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>expiry</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>ST 10D</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>ST 25D</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>RR 25D</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>RR 10D</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1" s="27">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>1W</t>
         </is>
@@ -4735,10 +4775,10 @@
         <f>C2*3</f>
         <v>0.5775</v>
       </c>
-      <c r="C2" s="29" t="n">
+      <c r="C2" s="30" t="n">
         <v>0.1925</v>
       </c>
-      <c r="D2" s="29" t="n">
+      <c r="D2" s="30" t="n">
         <v>-0.445</v>
       </c>
       <c r="E2" s="31">
@@ -4747,7 +4787,7 @@
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1" s="27">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>2W</t>
         </is>
@@ -4756,10 +4796,10 @@
         <f>C3*3</f>
         <v>0.6</v>
       </c>
-      <c r="C3" s="29" t="n">
+      <c r="C3" s="30" t="n">
         <v>0.2</v>
       </c>
-      <c r="D3" s="29" t="n">
+      <c r="D3" s="30" t="n">
         <v>-0.5</v>
       </c>
       <c r="E3" s="31">
@@ -4768,7 +4808,7 @@
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1" s="27">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>3W</t>
         </is>
@@ -4777,10 +4817,10 @@
         <f>C4*3</f>
         <v>0.585</v>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="30" t="n">
         <v>0.195</v>
       </c>
-      <c r="D4" s="29" t="n">
+      <c r="D4" s="30" t="n">
         <v>-0.595</v>
       </c>
       <c r="E4" s="31">
@@ -4789,7 +4829,7 @@
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1" s="27">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
@@ -4798,10 +4838,10 @@
         <f>C5*3.15</f>
         <v>0.693</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="30" t="n">
         <v>0.22</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="30" t="n">
         <v>-0.5825</v>
       </c>
       <c r="E5" s="31">
@@ -4810,7 +4850,7 @@
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1" s="27">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>2M</t>
         </is>
@@ -4819,10 +4859,10 @@
         <f>C6*3.15</f>
         <v>0.80325</v>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="30" t="n">
         <v>0.255</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="30" t="n">
         <v>-0.7425</v>
       </c>
       <c r="E6" s="31">
@@ -4831,7 +4871,7 @@
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1" s="27">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
@@ -4840,10 +4880,10 @@
         <f>C7*3.2</f>
         <v>0.928</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="30" t="n">
         <v>0.29</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="30" t="n">
         <v>-0.8075</v>
       </c>
       <c r="E7" s="31">
@@ -4852,7 +4892,7 @@
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1" s="27">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
@@ -4861,10 +4901,10 @@
         <f>C8*3.25</f>
         <v>1.18625</v>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="30" t="n">
         <v>0.365</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="30" t="n">
         <v>-0.9399999999999999</v>
       </c>
       <c r="E8" s="31">
@@ -4873,7 +4913,7 @@
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1" s="27">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>9M</t>
         </is>
@@ -4882,10 +4922,10 @@
         <f>C9*3.25</f>
         <v>1.3</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="30" t="n">
         <v>0.4</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="30" t="n">
         <v>-1.08</v>
       </c>
       <c r="E9" s="31">
@@ -4894,7 +4934,7 @@
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1" s="27">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
@@ -4903,10 +4943,10 @@
         <f>C10*3.4</f>
         <v>1.411</v>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="30" t="n">
         <v>0.415</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="30" t="n">
         <v>-1.12</v>
       </c>
       <c r="E10" s="31">
@@ -4915,7 +4955,7 @@
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1" s="27">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>2Y</t>
         </is>
@@ -4924,10 +4964,10 @@
         <f>C11*3.4</f>
         <v>1.462</v>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="30" t="n">
         <v>0.43</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="30" t="n">
         <v>-1.2</v>
       </c>
       <c r="E11" s="31">
@@ -4952,34 +4992,34 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.82421875" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1" s="27">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>expiry</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>ST 10D</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>ST 25D</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>RR 25D</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>RR 10D</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1" s="27">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>1W</t>
         </is>
@@ -4988,10 +5028,10 @@
         <f>C2*3.75</f>
         <v>0.825</v>
       </c>
-      <c r="C2" s="29" t="n">
+      <c r="C2" s="30" t="n">
         <v>0.22</v>
       </c>
-      <c r="D2" s="29" t="n">
+      <c r="D2" s="30" t="n">
         <v>0.48</v>
       </c>
       <c r="E2" s="31">
@@ -5000,7 +5040,7 @@
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1" s="27">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>2W</t>
         </is>
@@ -5009,10 +5049,10 @@
         <f>C3*3.75</f>
         <v>0.834375</v>
       </c>
-      <c r="C3" s="29" t="n">
+      <c r="C3" s="30" t="n">
         <v>0.2225</v>
       </c>
-      <c r="D3" s="29" t="n">
+      <c r="D3" s="30" t="n">
         <v>0.505</v>
       </c>
       <c r="E3" s="31">
@@ -5021,7 +5061,7 @@
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1" s="27">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>3W</t>
         </is>
@@ -5030,10 +5070,10 @@
         <f>C4*3.75</f>
         <v>0.84375</v>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="30" t="n">
         <v>0.225</v>
       </c>
-      <c r="D4" s="29" t="n">
+      <c r="D4" s="30" t="n">
         <v>0.52</v>
       </c>
       <c r="E4" s="31">
@@ -5042,7 +5082,7 @@
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1" s="27">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
@@ -5051,10 +5091,10 @@
         <f>C5*3.75</f>
         <v>0.871875</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="30" t="n">
         <v>0.2325</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="30" t="n">
         <v>0.555</v>
       </c>
       <c r="E5" s="31">
@@ -5063,7 +5103,7 @@
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1" s="27">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>2M</t>
         </is>
@@ -5072,10 +5112,10 @@
         <f>C6*3.75</f>
         <v>0.95625</v>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="30" t="n">
         <v>0.255</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="30" t="n">
         <v>0.5625</v>
       </c>
       <c r="E6" s="31">
@@ -5084,7 +5124,7 @@
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1" s="27">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
@@ -5093,10 +5133,10 @@
         <f>C7*3.85</f>
         <v>1.126125</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="30" t="n">
         <v>0.2925</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="30" t="n">
         <v>0.5775</v>
       </c>
       <c r="E7" s="31">
@@ -5105,7 +5145,7 @@
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1" s="27">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
@@ -5114,10 +5154,10 @@
         <f>C8*3.85</f>
         <v>1.318625</v>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="30" t="n">
         <v>0.3425</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="30" t="n">
         <v>0.5575</v>
       </c>
       <c r="E8" s="31">
@@ -5126,7 +5166,7 @@
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1" s="27">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>9M</t>
         </is>
@@ -5135,10 +5175,10 @@
         <f>C9*3.85</f>
         <v>1.52075</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="30" t="n">
         <v>0.395</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="30" t="n">
         <v>0.5875</v>
       </c>
       <c r="E9" s="31">
@@ -5147,7 +5187,7 @@
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1" s="27">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
@@ -5156,10 +5196,10 @@
         <f>C10*4</f>
         <v>1.6</v>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="30" t="n">
         <v>0.4</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="30" t="n">
         <v>0.58</v>
       </c>
       <c r="E10" s="31">
@@ -5168,7 +5208,7 @@
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1" s="27">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>2Y</t>
         </is>
@@ -5177,10 +5217,10 @@
         <f>C11*4.1</f>
         <v>1.71175</v>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="30" t="n">
         <v>0.4175</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="30" t="n">
         <v>0.6625</v>
       </c>
       <c r="E11" s="31">
@@ -5205,34 +5245,34 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.82421875" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1" s="27">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>expiry</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>ST 10D</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>ST 25D</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>RR 25D</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>RR 10D</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1" s="27">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>1W</t>
         </is>
@@ -5241,10 +5281,10 @@
         <f>C2*3.1</f>
         <v>0.33325</v>
       </c>
-      <c r="C2" s="29" t="n">
+      <c r="C2" s="30" t="n">
         <v>0.1075</v>
       </c>
-      <c r="D2" s="29" t="n">
+      <c r="D2" s="30" t="n">
         <v>0.34</v>
       </c>
       <c r="E2" s="31">
@@ -5253,7 +5293,7 @@
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1" s="27">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>2W</t>
         </is>
@@ -5262,10 +5302,10 @@
         <f>C3*3.1</f>
         <v>0.3875</v>
       </c>
-      <c r="C3" s="29" t="n">
+      <c r="C3" s="30" t="n">
         <v>0.125</v>
       </c>
-      <c r="D3" s="29" t="n">
+      <c r="D3" s="30" t="n">
         <v>0.39</v>
       </c>
       <c r="E3" s="31">
@@ -5274,7 +5314,7 @@
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1" s="27">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>3W</t>
         </is>
@@ -5283,10 +5323,10 @@
         <f>C4*3.1</f>
         <v>0.465</v>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="30" t="n">
         <v>0.15</v>
       </c>
-      <c r="D4" s="29" t="n">
+      <c r="D4" s="30" t="n">
         <v>0.425</v>
       </c>
       <c r="E4" s="31">
@@ -5295,7 +5335,7 @@
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1" s="27">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
@@ -5304,10 +5344,10 @@
         <f>C5*3.1</f>
         <v>0.403</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="30" t="n">
         <v>0.13</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="30" t="n">
         <v>0.49</v>
       </c>
       <c r="E5" s="31">
@@ -5316,7 +5356,7 @@
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1" s="27">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>2M</t>
         </is>
@@ -5325,10 +5365,10 @@
         <f>C6*3.1</f>
         <v>0.4805</v>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="30" t="n">
         <v>0.155</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="30" t="n">
         <v>0.575</v>
       </c>
       <c r="E6" s="31">
@@ -5337,7 +5377,7 @@
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1" s="27">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
@@ -5346,10 +5386,10 @@
         <f>C7*3.1</f>
         <v>0.558</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="30" t="n">
         <v>0.18</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="30" t="n">
         <v>0.6475</v>
       </c>
       <c r="E7" s="31">
@@ -5358,7 +5398,7 @@
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1" s="27">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
@@ -5367,10 +5407,10 @@
         <f>C8*3.1</f>
         <v>0.72075</v>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="30" t="n">
         <v>0.2325</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="30" t="n">
         <v>0.7875</v>
       </c>
       <c r="E8" s="31">
@@ -5379,7 +5419,7 @@
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1" s="27">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>9M</t>
         </is>
@@ -5388,10 +5428,10 @@
         <f>C9*3.1</f>
         <v>0.79825</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="30" t="n">
         <v>0.2575</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="30" t="n">
         <v>0.8625</v>
       </c>
       <c r="E9" s="31">
@@ -5400,7 +5440,7 @@
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1" s="27">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
@@ -5409,10 +5449,10 @@
         <f>C10*3.2</f>
         <v>0.84</v>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="30" t="n">
         <v>0.2625</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="30" t="n">
         <v>0.9125</v>
       </c>
       <c r="E10" s="31">
@@ -5421,7 +5461,7 @@
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1" s="27">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>2Y</t>
         </is>
@@ -5430,10 +5470,10 @@
         <f>C11*3.2</f>
         <v>1.08</v>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="30" t="n">
         <v>0.3375</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="30" t="n">
         <v>0.8675</v>
       </c>
       <c r="E11" s="31">
@@ -5692,34 +5732,34 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.82421875" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1" s="27">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>expiry</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>ST 10D</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>ST 25D</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>RR 25D</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>RR 10D</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1" s="27">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>1W</t>
         </is>
@@ -5728,10 +5768,10 @@
         <f>C2*3.75</f>
         <v>0.703125</v>
       </c>
-      <c r="C2" s="29" t="n">
+      <c r="C2" s="30" t="n">
         <v>0.1875</v>
       </c>
-      <c r="D2" s="29" t="n">
+      <c r="D2" s="30" t="n">
         <v>0.095</v>
       </c>
       <c r="E2" s="31">
@@ -5740,7 +5780,7 @@
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1" s="27">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>2W</t>
         </is>
@@ -5749,10 +5789,10 @@
         <f>C3*3.75</f>
         <v>0.73125</v>
       </c>
-      <c r="C3" s="29" t="n">
+      <c r="C3" s="30" t="n">
         <v>0.195</v>
       </c>
-      <c r="D3" s="29" t="n">
+      <c r="D3" s="30" t="n">
         <v>0.14</v>
       </c>
       <c r="E3" s="31">
@@ -5761,7 +5801,7 @@
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1" s="27">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>3W</t>
         </is>
@@ -5770,10 +5810,10 @@
         <f>C4*3.75</f>
         <v>0.75</v>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="30" t="n">
         <v>0.2</v>
       </c>
-      <c r="D4" s="29" t="n">
+      <c r="D4" s="30" t="n">
         <v>0.145</v>
       </c>
       <c r="E4" s="31">
@@ -5782,7 +5822,7 @@
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1" s="27">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
@@ -5791,10 +5831,10 @@
         <f>C5*3.75</f>
         <v>0.75</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="30" t="n">
         <v>0.2</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="30" t="n">
         <v>0.1575</v>
       </c>
       <c r="E5" s="31">
@@ -5803,7 +5843,7 @@
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1" s="27">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>2M</t>
         </is>
@@ -5812,10 +5852,10 @@
         <f>C6*3.75</f>
         <v>0.834375</v>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="30" t="n">
         <v>0.2225</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="30" t="n">
         <v>0.185</v>
       </c>
       <c r="E6" s="31">
@@ -5824,7 +5864,7 @@
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1" s="27">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
@@ -5833,10 +5873,10 @@
         <f>C7*3.85</f>
         <v>1.001</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="30" t="n">
         <v>0.26</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="30" t="n">
         <v>0.23</v>
       </c>
       <c r="E7" s="31">
@@ -5845,7 +5885,7 @@
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1" s="27">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
@@ -5854,10 +5894,10 @@
         <f>C8*3.85</f>
         <v>1.155</v>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="30" t="n">
         <v>0.3</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="30" t="n">
         <v>0.355</v>
       </c>
       <c r="E8" s="31">
@@ -5866,7 +5906,7 @@
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1" s="27">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>9M</t>
         </is>
@@ -5875,10 +5915,10 @@
         <f>C9*3.85</f>
         <v>1.36675</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="30" t="n">
         <v>0.355</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="30" t="n">
         <v>0.375</v>
       </c>
       <c r="E9" s="31">
@@ -5887,7 +5927,7 @@
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1" s="27">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
@@ -5896,10 +5936,10 @@
         <f>C10*4</f>
         <v>1.45</v>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="30" t="n">
         <v>0.3625</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="30" t="n">
         <v>0.46</v>
       </c>
       <c r="E10" s="31">
@@ -5908,7 +5948,7 @@
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1" s="27">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>2Y</t>
         </is>
@@ -5917,10 +5957,10 @@
         <f>C11*4.1</f>
         <v>1.64</v>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="30" t="n">
         <v>0.4</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="30" t="n">
         <v>0.435</v>
       </c>
       <c r="E11" s="31">
